--- a/docs/Unit_Test_Plan_v0.1 (1).xlsx
+++ b/docs/Unit_Test_Plan_v0.1 (1).xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="65">
   <si>
     <t>Actual Result</t>
   </si>
@@ -117,6 +117,117 @@
   </si>
   <si>
     <t>Relevant document chunks should be returned with their source names.</t>
+  </si>
+  <si>
+    <t>test_scope_extraction</t>
+  </si>
+  <si>
+    <t>Upload project SRS and project plan documents and ask for project scope, goals, deliverables and milestones.</t>
+  </si>
+  <si>
+    <t>Check whether the Scope Extraction Agent extracts project information only from retrieved documents.</t>
+  </si>
+  <si>
+    <t>Project goal, scope, deliverables and milestones should be extracted correctly.</t>
+  </si>
+  <si>
+    <t>test_milestone_extraction</t>
+  </si>
+  <si>
+    <t>Upload a project plan containing a milestone table and ask for milestone details.</t>
+  </si>
+  <si>
+    <t>Check whether milestone name, target date, responsible team and status are extracted.</t>
+  </si>
+  <si>
+    <t>All milestone rows should be extracted with correct dates, teams and status.</t>
+  </si>
+  <si>
+    <t>test_responsibility_extraction</t>
+  </si>
+  <si>
+    <t>Upload an SRS containing team responsibilities and ask for project responsibilities.</t>
+  </si>
+  <si>
+    <t>Check whether responsible teams and their responsibilities are extracted.</t>
+  </si>
+  <si>
+    <t>Responsibilities should be extracted from the provided project context without invention.</t>
+  </si>
+  <si>
+    <t>needs_validation</t>
+  </si>
+  <si>
+    <t>test_risk_detection</t>
+  </si>
+  <si>
+    <t>Upload a weekly project status report containing documented project risks and ask for major risks.</t>
+  </si>
+  <si>
+    <t>Check whether the Risk Detection Agent identifies risks supported by the project documents.</t>
+  </si>
+  <si>
+    <t>Documented risks should be identified with risk type, probability, impact and recommended action.</t>
+  </si>
+  <si>
+    <t>test_delivery_forecasting</t>
+  </si>
+  <si>
+    <t>Upload a project status report containing progress, delays and dependencies and ask whether the project is on track.</t>
+  </si>
+  <si>
+    <t>Check whether the delivery forecast is based on documented project evidence.</t>
+  </si>
+  <si>
+    <t>The agent should return On Track, At Risk or Delayed with supporting reasoning.</t>
+  </si>
+  <si>
+    <t>test_blocker_action_identification</t>
+  </si>
+  <si>
+    <t>Upload project meeting notes containing blockers and action items and ask for current blockers and actions.</t>
+  </si>
+  <si>
+    <t>Check whether current blockers and action items are distinguished correctly.</t>
+  </si>
+  <si>
+    <t>Blockers and action items should be extracted with available responsible team, due date and status.</t>
+  </si>
+  <si>
+    <t>test_pending_decision_identification</t>
+  </si>
+  <si>
+    <t>Upload meeting notes containing an explicitly unresolved decision and ask for pending decisions.</t>
+  </si>
+  <si>
+    <t>Check whether only explicitly pending decisions are identified.</t>
+  </si>
+  <si>
+    <t>Only unresolved decisions should be returned; deadlines or risks should not be classified as decisions.</t>
+  </si>
+  <si>
+    <t>test_multidocument_retrieval</t>
+  </si>
+  <si>
+    <t>Upload SRS, project plan, meeting notes, status report and technical design documents together and ask a project-related question.</t>
+  </si>
+  <si>
+    <t>Check whether relevant information is retrieved from multiple uploaded documents.</t>
+  </si>
+  <si>
+    <t>Relevant chunks from the uploaded project documents should be retrieved and used by the agents.</t>
+  </si>
+  <si>
+    <t>test_no_hallucination</t>
+  </si>
+  <si>
+    <t>Upload project documents that do not contain blockers or pending decisions and ask for blockers and decisions.</t>
+  </si>
+  <si>
+    <t>Check whether the agent avoids creating information that is not present in the documents.</t>
+  </si>
+  <si>
+    <t>Blockers and pending decisions should return as empty lists when none are explicitly present.</t>
   </si>
 </sst>
 </file>
@@ -511,7 +622,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.109375" customWidth="1"/>
@@ -642,6 +753,186 @@
         <v>22</v>
       </c>
     </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" t="s">
+        <v>55</v>
+      </c>
+      <c r="E13" t="s">
+        <v>56</v>
+      </c>
+      <c r="F13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>61</v>
+      </c>
+      <c r="C15" t="s">
+        <v>62</v>
+      </c>
+      <c r="D15" t="s">
+        <v>63</v>
+      </c>
+      <c r="E15" t="s">
+        <v>64</v>
+      </c>
+      <c r="F15" t="s">
+        <v>40</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/docs/Unit_Test_Plan_v0.1 (1).xlsx
+++ b/docs/Unit_Test_Plan_v0.1 (1).xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SIRISRI\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI-Project-Intelligence-Risk-Advisor\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9264"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19368" windowHeight="9252"/>
   </bookViews>
   <sheets>
     <sheet name="UT" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="120">
   <si>
     <t>Actual Result</t>
   </si>
@@ -155,9 +155,6 @@
     <t>Responsibilities should be extracted from the provided project context without invention.</t>
   </si>
   <si>
-    <t>needs_validation</t>
-  </si>
-  <si>
     <t>test_risk_detection</t>
   </si>
   <si>
@@ -228,6 +225,174 @@
   </si>
   <si>
     <t>Blockers and pending decisions should return as empty lists when none are explicitly present.</t>
+  </si>
+  <si>
+    <t>test_agent_routing</t>
+  </si>
+  <si>
+    <t>Ask a scope related question</t>
+  </si>
+  <si>
+    <t>Check correct agent routing</t>
+  </si>
+  <si>
+    <t>Question should reach Scope Agent</t>
+  </si>
+  <si>
+    <t>test_conversational_ai</t>
+  </si>
+  <si>
+    <t>Ask a project question in chat</t>
+  </si>
+  <si>
+    <t>Check AI response generation</t>
+  </si>
+  <si>
+    <t>Relevant response should be displayed</t>
+  </si>
+  <si>
+    <t>test_conversation_context</t>
+  </si>
+  <si>
+    <t>Ask a follow-up question</t>
+  </si>
+  <si>
+    <t>Check previous context retention</t>
+  </si>
+  <si>
+    <t>Follow-up should use previous context</t>
+  </si>
+  <si>
+    <t>test_multi_turn_chat</t>
+  </si>
+  <si>
+    <t>Ask multiple related questions</t>
+  </si>
+  <si>
+    <t>Check multi-turn conversation</t>
+  </si>
+  <si>
+    <t>Responses should remain consistent</t>
+  </si>
+  <si>
+    <t>test_react_chat</t>
+  </si>
+  <si>
+    <t>Ask a question from React UI</t>
+  </si>
+  <si>
+    <t>Check chat interface response</t>
+  </si>
+  <si>
+    <t>Question and response should display correctly</t>
+  </si>
+  <si>
+    <t>test_api_communication</t>
+  </si>
+  <si>
+    <t>Send question from frontend</t>
+  </si>
+  <si>
+    <t>Check frontend-backend communication</t>
+  </si>
+  <si>
+    <t>API should return valid response</t>
+  </si>
+  <si>
+    <t>test_agent_integration</t>
+  </si>
+  <si>
+    <t>Ask scope risk and blocker questions</t>
+  </si>
+  <si>
+    <t>Check agent response integration</t>
+  </si>
+  <si>
+    <t>Correct agent result should be displayed</t>
+  </si>
+  <si>
+    <t>test_multiple_documents</t>
+  </si>
+  <si>
+    <t>Upload multiple project documents</t>
+  </si>
+  <si>
+    <t>Check retrieval across documents</t>
+  </si>
+  <si>
+    <t>Relevant information should be retrieved</t>
+  </si>
+  <si>
+    <t>test_source_grounding</t>
+  </si>
+  <si>
+    <t>Ask a question from uploaded documents</t>
+  </si>
+  <si>
+    <t>Check response grounding</t>
+  </si>
+  <si>
+    <t>Response should use document information</t>
+  </si>
+  <si>
+    <t>test_unknown_question</t>
+  </si>
+  <si>
+    <t>Ask unavailable project question</t>
+  </si>
+  <si>
+    <t>Check unsupported information handling</t>
+  </si>
+  <si>
+    <t>Assistant should indicate information unavailable</t>
+  </si>
+  <si>
+    <t>test_empty_query</t>
+  </si>
+  <si>
+    <t>Submit an empty message</t>
+  </si>
+  <si>
+    <t>Check empty input validation</t>
+  </si>
+  <si>
+    <t>Empty message should be rejected</t>
+  </si>
+  <si>
+    <t>test_invalid_file_upload</t>
+  </si>
+  <si>
+    <t>Upload unsupported file type</t>
+  </si>
+  <si>
+    <t>Check file validation</t>
+  </si>
+  <si>
+    <t>Invalid file should be rejected</t>
+  </si>
+  <si>
+    <t>test_backend_error</t>
+  </si>
+  <si>
+    <t>Send request when backend is unavailable</t>
+  </si>
+  <si>
+    <t>Check error handling</t>
+  </si>
+  <si>
+    <t>Clear error message should be displayed</t>
+  </si>
+  <si>
+    <t>test_end_to_end_assistant</t>
+  </si>
+  <si>
+    <t>Upload documents and ask project questions</t>
+  </si>
+  <si>
+    <t>Check complete assistant workflow</t>
+  </si>
+  <si>
+    <t>System should return correct project response</t>
   </si>
 </sst>
 </file>
@@ -622,12 +787,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.109375" customWidth="1"/>
-    <col min="2" max="2" width="20.5546875" customWidth="1"/>
-    <col min="3" max="3" width="47.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.5546875" customWidth="1"/>
+    <col min="2" max="2" width="37" customWidth="1"/>
+    <col min="3" max="3" width="56.109375" customWidth="1"/>
     <col min="4" max="4" width="62.6640625" customWidth="1"/>
     <col min="5" max="5" width="35.21875" customWidth="1"/>
     <col min="6" max="6" width="15.88671875" customWidth="1"/>
@@ -810,7 +975,7 @@
         <v>39</v>
       </c>
       <c r="F9" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -818,16 +983,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" t="s">
         <v>41</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>42</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>43</v>
-      </c>
-      <c r="E10" t="s">
-        <v>44</v>
       </c>
       <c r="F10" t="s">
         <v>22</v>
@@ -838,16 +1003,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" t="s">
         <v>45</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>46</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>47</v>
-      </c>
-      <c r="E11" t="s">
-        <v>48</v>
       </c>
       <c r="F11" t="s">
         <v>22</v>
@@ -858,16 +1023,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" t="s">
         <v>49</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>50</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>51</v>
-      </c>
-      <c r="E12" t="s">
-        <v>52</v>
       </c>
       <c r="F12" t="s">
         <v>22</v>
@@ -878,19 +1043,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" t="s">
         <v>53</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>54</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>55</v>
       </c>
-      <c r="E13" t="s">
-        <v>56</v>
-      </c>
       <c r="F13" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -898,16 +1063,16 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" t="s">
         <v>57</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>58</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>59</v>
-      </c>
-      <c r="E14" t="s">
-        <v>60</v>
       </c>
       <c r="F14" t="s">
         <v>22</v>
@@ -918,19 +1083,299 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" t="s">
         <v>61</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>62</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>63</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
         <v>64</v>
       </c>
-      <c r="F15" t="s">
-        <v>40</v>
+      <c r="C16" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" t="s">
+        <v>66</v>
+      </c>
+      <c r="E16" t="s">
+        <v>67</v>
+      </c>
+      <c r="F16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>68</v>
+      </c>
+      <c r="C17" t="s">
+        <v>69</v>
+      </c>
+      <c r="D17" t="s">
+        <v>70</v>
+      </c>
+      <c r="E17" t="s">
+        <v>71</v>
+      </c>
+      <c r="F17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" t="s">
+        <v>73</v>
+      </c>
+      <c r="D18" t="s">
+        <v>74</v>
+      </c>
+      <c r="E18" t="s">
+        <v>75</v>
+      </c>
+      <c r="F18" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" t="s">
+        <v>77</v>
+      </c>
+      <c r="D19" t="s">
+        <v>78</v>
+      </c>
+      <c r="E19" t="s">
+        <v>79</v>
+      </c>
+      <c r="F19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20" t="s">
+        <v>81</v>
+      </c>
+      <c r="D20" t="s">
+        <v>82</v>
+      </c>
+      <c r="E20" t="s">
+        <v>83</v>
+      </c>
+      <c r="F20" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21" t="s">
+        <v>85</v>
+      </c>
+      <c r="D21" t="s">
+        <v>86</v>
+      </c>
+      <c r="E21" t="s">
+        <v>87</v>
+      </c>
+      <c r="F21" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22" t="s">
+        <v>89</v>
+      </c>
+      <c r="D22" t="s">
+        <v>90</v>
+      </c>
+      <c r="E22" t="s">
+        <v>91</v>
+      </c>
+      <c r="F22" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>92</v>
+      </c>
+      <c r="C23" t="s">
+        <v>93</v>
+      </c>
+      <c r="D23" t="s">
+        <v>94</v>
+      </c>
+      <c r="E23" t="s">
+        <v>95</v>
+      </c>
+      <c r="F23" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>96</v>
+      </c>
+      <c r="C24" t="s">
+        <v>97</v>
+      </c>
+      <c r="D24" t="s">
+        <v>98</v>
+      </c>
+      <c r="E24" t="s">
+        <v>99</v>
+      </c>
+      <c r="F24" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>100</v>
+      </c>
+      <c r="C25" t="s">
+        <v>101</v>
+      </c>
+      <c r="D25" t="s">
+        <v>102</v>
+      </c>
+      <c r="E25" t="s">
+        <v>103</v>
+      </c>
+      <c r="F25" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>104</v>
+      </c>
+      <c r="C26" t="s">
+        <v>105</v>
+      </c>
+      <c r="D26" t="s">
+        <v>106</v>
+      </c>
+      <c r="E26" t="s">
+        <v>107</v>
+      </c>
+      <c r="F26" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>108</v>
+      </c>
+      <c r="C27" t="s">
+        <v>109</v>
+      </c>
+      <c r="D27" t="s">
+        <v>110</v>
+      </c>
+      <c r="E27" t="s">
+        <v>111</v>
+      </c>
+      <c r="F27" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>112</v>
+      </c>
+      <c r="C28" t="s">
+        <v>113</v>
+      </c>
+      <c r="D28" t="s">
+        <v>114</v>
+      </c>
+      <c r="E28" t="s">
+        <v>115</v>
+      </c>
+      <c r="F28" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>116</v>
+      </c>
+      <c r="C29" t="s">
+        <v>117</v>
+      </c>
+      <c r="D29" t="s">
+        <v>118</v>
+      </c>
+      <c r="E29" t="s">
+        <v>119</v>
+      </c>
+      <c r="F29" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
